--- a/AAII_Financials/Quarterly/AFLYY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFLYY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
   <si>
     <t>AFLYY</t>
   </si>
@@ -656,72 +656,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -758,8 +762,11 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -796,8 +803,11 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -834,8 +844,11 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -850,8 +863,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -888,8 +902,11 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,8 +943,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -964,8 +984,11 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1002,8 +1025,11 @@
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1015,8 +1041,9 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1053,8 +1080,11 @@
       <c r="N17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1091,8 +1121,11 @@
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,8 +1140,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1145,8 +1179,11 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1183,8 +1220,11 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1221,8 +1261,11 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1259,8 +1302,11 @@
       <c r="N23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1297,8 +1343,11 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1335,8 +1384,11 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1373,8 +1425,11 @@
       <c r="N26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1411,8 +1466,11 @@
       <c r="N27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1449,8 +1507,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1487,8 +1548,11 @@
       <c r="N29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1525,8 +1589,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1563,8 +1630,11 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1601,8 +1671,11 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1639,8 +1712,11 @@
       <c r="N33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1677,8 +1753,11 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1715,51 +1794,57 @@
       <c r="N35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1774,8 +1859,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1790,350 +1876,378 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5816300</v>
+      </c>
+      <c r="E41" s="3">
         <v>6826900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5534800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5875900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5695800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4952400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4999500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5078100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5665900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5878700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6846500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6859700</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>996200</v>
       </c>
       <c r="E42" s="3">
+        <v>1528900</v>
+      </c>
+      <c r="F42" s="3">
         <v>1262200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1545200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1719300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1342400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>961800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1288200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1265400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1376600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1390500</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3179500</v>
+      </c>
+      <c r="E43" s="3">
         <v>3376000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3179500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2880400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2823300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2661000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2670000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2474900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2689400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2688500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2854000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2469300</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1215600</v>
+      </c>
+      <c r="E44" s="3">
         <v>1186400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1164700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1165100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1166200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1048400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>992900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1057300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>981500</v>
-      </c>
-      <c r="L44" s="3">
-        <v>942900</v>
       </c>
       <c r="M44" s="3">
         <v>942900</v>
       </c>
       <c r="N44" s="3">
+        <v>942900</v>
+      </c>
+      <c r="O44" s="3">
         <v>845700</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4605100</v>
+        <v>2424300</v>
       </c>
       <c r="E45" s="3">
+        <v>3076200</v>
+      </c>
+      <c r="F45" s="3">
         <v>982700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1419700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1617100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1631000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1060200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1543600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1884700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1658200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>736200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2293600</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13631900</v>
+      </c>
+      <c r="E46" s="3">
         <v>15994500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12401100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12886300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13021700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11635300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10958700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11442100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12486900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12545000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13059600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12468200</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>268500</v>
+      </c>
+      <c r="E47" s="3">
         <v>284800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1345500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>301500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>240800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>229100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1278600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>267700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>143600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>144600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1163900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>134400</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>29012900</v>
+      </c>
+      <c r="E48" s="3">
         <v>28747800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>29097100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>28168500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>27549000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>24231500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22230000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>23153000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21570800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20483300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20877600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>19338500</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1649700</v>
+      </c>
+      <c r="E49" s="3">
         <v>1652300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1986600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1994600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2158500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1853700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1646100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1512400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1450800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1785500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1663500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1408800</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2170,8 +2284,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2208,46 +2325,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2281500</v>
+      </c>
+      <c r="E52" s="3">
         <v>2241400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>352200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1503000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1456300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1722900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>410000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1830200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1729300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1623700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>339300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1863900</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2284,46 +2407,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>47534600</v>
+      </c>
+      <c r="E54" s="3">
         <v>49451200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>46313300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>45210600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>45034600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>40484200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>37431400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>38922600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>38252400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>37472200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>38123100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>35825600</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2338,8 +2467,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2354,236 +2484,255 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3452500</v>
+      </c>
+      <c r="E57" s="3">
         <v>3432500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3197100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3052900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2954800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2765900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2700100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2840700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2783700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2834200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2704800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2979500</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2187800</v>
+      </c>
+      <c r="E58" s="3">
         <v>3678100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3242900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3035300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3410500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2137900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2768400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2735900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2839400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3060700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2791000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2477800</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11647400</v>
+      </c>
+      <c r="E59" s="3">
         <v>11990100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10689200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10564400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12102200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11226800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8991600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9846100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10443600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10360300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8914600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9628500</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>20214800</v>
+      </c>
+      <c r="E60" s="3">
         <v>22353300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20092800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19675000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>21570200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19027200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>16845400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>18001300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18644600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>18972900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>17629000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>17109400</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15376400</v>
+      </c>
+      <c r="E61" s="3">
         <v>15200000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14987700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>14568800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>13360000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>13040400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12412300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12333300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11860100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11009800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>12305700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11548500</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6590900</v>
+      </c>
+      <c r="E62" s="3">
         <v>6145500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6262800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6152800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6326500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5683100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5568900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5670300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5549100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5469800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5737800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5979000</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2620,8 +2769,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2658,8 +2810,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2696,46 +2851,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>44350500</v>
+      </c>
+      <c r="E66" s="3">
         <v>45886100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>43537600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>42627000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>43497400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>39770900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>36604200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>37925500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>37891400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>37320100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>37570500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>36422500</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2750,8 +2911,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2788,8 +2950,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2826,8 +2991,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2864,8 +3032,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2902,46 +3073,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="3">
         <v>1952600</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J72" s="3">
         <v>400700</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N72" s="3">
         <v>1109800</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2978,8 +3155,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3016,8 +3196,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3054,46 +3237,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>743700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1144900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>349900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>89200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-958300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-2102200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1826300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1919500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-2464400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-2645400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-2267000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-1681800</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3130,51 +3319,57 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3211,8 +3406,11 @@
       <c r="N81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3227,46 +3425,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>892500</v>
+      </c>
+      <c r="E83" s="3">
         <v>772800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>574600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>775200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>698600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>677500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>573700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>649900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>662700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>662800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>565400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>618700</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3303,8 +3505,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3341,8 +3546,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3379,8 +3587,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3417,8 +3628,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3455,46 +3669,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1137900</v>
+      </c>
+      <c r="E89" s="3">
         <v>1870200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1190600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1189700</v>
       </c>
-      <c r="G89" s="3">
-        <v>1317700</v>
-      </c>
       <c r="H89" s="3">
+        <v>1397500</v>
+      </c>
+      <c r="I89" s="3">
         <v>2059000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>960800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1023900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>944000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>829600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-287400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>673200</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3509,46 +3729,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-959700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1083800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1300900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1327000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1170900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1311100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-825100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1098600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1384300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-705600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1404900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1034100</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3585,8 +3809,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3623,46 +3850,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-42300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-932800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-701000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-715700</v>
       </c>
-      <c r="G94" s="3">
-        <v>-939500</v>
-      </c>
       <c r="H94" s="3">
+        <v>-1089800</v>
+      </c>
+      <c r="I94" s="3">
         <v>-910100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-521800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-962500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-923600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-581500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1398300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-641400</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3677,46 +3910,50 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E96" s="3">
         <v>63400</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3">
         <v>89200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>7000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>64900</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K96" s="3">
         <v>78100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>5400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>61500</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3">
         <v>37000</v>
       </c>
     </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3753,8 +3990,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3791,8 +4031,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3829,118 +4072,130 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2062200</v>
+      </c>
+      <c r="E100" s="3">
         <v>437000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-839500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-248700</v>
       </c>
-      <c r="G100" s="3">
-        <v>-85700</v>
-      </c>
       <c r="H100" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="I100" s="3">
         <v>-1395400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-183200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-855500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-165000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1096100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1383900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>294200</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-22700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>31100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-15600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-30000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>49600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-28700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>9500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>6600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-33700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-33100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-949400</v>
+      </c>
+      <c r="E102" s="3">
         <v>1391700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-345200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>220600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>281900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-269100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>286800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-809700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-174600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-798400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-330500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>335500</v>
       </c>
     </row>
